--- a/AAII_Financials/Quarterly/STBFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STBFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>STBFY</t>
   </si>
@@ -656,78 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,8 +771,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,8 +815,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,8 +859,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,8 +879,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +921,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,8 +965,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -989,8 +1009,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1030,8 +1053,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,8 +1070,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1085,8 +1112,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,8 +1156,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,8 +1176,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1184,8 +1218,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1225,8 +1262,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1266,8 +1306,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1307,8 +1350,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1348,8 +1394,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,8 +1438,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1430,8 +1482,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1471,8 +1526,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1570,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1614,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1658,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,8 +1702,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1676,8 +1746,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1717,8 +1790,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,8 +1834,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1799,54 +1878,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1947,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,73 +1965,77 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>983200</v>
+      </c>
+      <c r="E41" s="3">
         <v>948200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1011100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1020800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>964300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1022100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1218400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>990000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1271500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>990000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1271500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1370200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1521400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>17300</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>29000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>11800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -1959,297 +2049,321 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2613900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2674500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2624400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2257600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2325300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2101700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2295400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2441000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2304700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2441000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2304700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1999900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2148100</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>990800</v>
+      </c>
+      <c r="E44" s="3">
         <v>877200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1028000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>753200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>852600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>837400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>822700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>818500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>922400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>818500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>922400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>922800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>804500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>290400</v>
+      </c>
+      <c r="E45" s="3">
         <v>37400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>279600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>276700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>267900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>104400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>211300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>218600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>211300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>218600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>227800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4878400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4637800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4943200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4201400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4418900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4229100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4532500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4460800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4717200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4460800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4717200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4520700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4598100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E47" s="3">
         <v>96600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>151900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>142800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>154600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>103500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>177200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>185400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>177200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>185400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>182100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3625600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3735700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3720600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3456600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3253400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3276800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3323500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3070500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3140200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3070500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3140200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3259600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3263400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5352800</v>
+      </c>
+      <c r="E49" s="3">
         <v>5519000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5635400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5190900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5208900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5290400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5487800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5227500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5394300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5227500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5394300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5499500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5437200</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2403,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,32 +2447,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>46000</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>48200</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>55900</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
@@ -2369,10 +2489,13 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,49 +2535,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14118900</v>
+      </c>
+      <c r="E54" s="3">
         <v>14146600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14581100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13090100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13136200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13061200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13566900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12972100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13485900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12972100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13485900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13511500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13523200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2599,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,254 +2617,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3266800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1238900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3336400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1155400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2925500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2804700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1291300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3063200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3049900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3063200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3049900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2831200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1209400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E58" s="3">
         <v>189100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>330300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>254300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>305400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>358100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>435500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>349400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>491200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>349400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>491200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>428800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>530300</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>357200</v>
+      </c>
+      <c r="E59" s="3">
         <v>261600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>368900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>280200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>363100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>327600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>308800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>346900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>375300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>346900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>375300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>434600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>378100</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3719700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3662300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4035600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3461200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3593900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3490300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3800500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3759500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3916300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3759500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3916300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3694600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3823100</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E61" s="3">
         <v>318000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>288100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>159100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>169700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>415300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>167400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>311100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>167400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>311100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>488400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>750700</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>468600</v>
+      </c>
+      <c r="E62" s="3">
         <v>204000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>493200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>167800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>418500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>442900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>176300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>384500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>404800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>384500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>404800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>414300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2923,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2967,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,49 +3011,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5052700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5056600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5422800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4724300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4965900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4897800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5160200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5051200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5383900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5051200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5383900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5354200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5484400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3075,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3117,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3161,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3037,8 +3205,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,49 +3249,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4864700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4894400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5117900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4560000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4269700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4367500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4630400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4265300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4293400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4265300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4293400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4488600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4510200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3337,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3381,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,49 +3425,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8331600</v>
+      </c>
+      <c r="E76" s="3">
         <v>8393200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8450800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7693600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7469200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7456200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7713900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7250900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7350600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7250900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7350600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7395700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7319300</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,54 +3513,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3411,8 +3606,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,49 +3626,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E83" s="3">
         <v>121500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>74800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>116700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>124100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>134900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>59900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>129700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>129600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>129700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>129600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>144000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3712,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3756,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3800,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3844,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,49 +3888,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E89" s="3">
         <v>278200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>211200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>342000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>223900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>442000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>350900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>214300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>350900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>214300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>94700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>145700</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,49 +3952,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-113700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-215400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-159800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-195500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-190700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-154000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-201900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-121300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-124000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-121300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-124000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-110900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-146900</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4038,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,49 +4082,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-113500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-204300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-157100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-189200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-138300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-198600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-121600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-120700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-121600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-120700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-106800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-141400</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,8 +4146,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3931,19 +4165,19 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>81700</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>82800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
+      <c r="L96" s="3">
+        <v>0</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>4</v>
@@ -3954,8 +4188,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4232,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4276,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,127 +4320,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-40800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>76600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-94200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-75300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-73500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-455800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-134100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-455800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-134100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-132200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E101" s="3">
         <v>21900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>52200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>50100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>50100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>35600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E102" s="3">
         <v>46700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>135600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>80700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-122100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>178700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-240900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-240900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-139100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-49300</v>
       </c>
     </row>
